--- a/frontend/public/templates/Warehouse_Master_Import_Template.xlsx
+++ b/frontend/public/templates/Warehouse_Master_Import_Template.xlsx
@@ -976,7 +976,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -984,7 +983,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1354,7 +1352,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>One of: Ground/Floor, SPR, Drive-in, Mix. Fill on a row to record one storage-type entry for this warehouse — use multiple rows (same Location Code) to break a warehouse down by storage type, each with its own Category, Pallet Positions, and dimensions. Don't combine "Mix" with specific storage-type rows for the same warehouse — pick one approach per warehouse.</t>
+          <t>One of: Ground/Floor, SPR, Drive-in, Stillage, Mix. Fill on a row to record one storage-type entry for this warehouse — use multiple rows (same Location Code) to break a warehouse down by storage type, each with its own Category, Pallet Positions, and dimensions. Don't combine "Mix" with specific storage-type rows for the same warehouse — pick one approach per warehouse.</t>
         </is>
       </c>
     </row>
